--- a/docs/tutorials/files/xslope_block_wall_start.xlsx
+++ b/docs/tutorials/files/xslope_block_wall_start.xlsx
@@ -13551,7 +13551,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>0.0</v>
+        <v>-0.2978258814</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>

--- a/docs/tutorials/files/xslope_block_wall_start.xlsx
+++ b/docs/tutorials/files/xslope_block_wall_start.xlsx
@@ -13539,20 +13539,10 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>10.6</v>
-      </c>
-      <c r="C3" s="3">
-        <v>11.2</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E3" s="3">
-        <v>-0.2978258814</v>
-      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
